--- a/src/test/resources/response.xlsx
+++ b/src/test/resources/response.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="81">
   <si>
     <t>Response</t>
   </si>
@@ -45,195 +45,174 @@
     <t>Jobid</t>
   </si>
   <si>
-    <t>019da9be-5abf-71c5-b556-808eb736e04e</t>
+    <t>019daebe-4481-7062-bf05-01ad34b53c45</t>
   </si>
   <si>
     <t>{
     "message": "Crawl job created successfully.",
-    "jobId": "019da9be-5abf-71c5-b556-808eb736e04e"
-}</t>
-  </si>
-  <si>
-    <t>019da9be-6063-7182-8ffe-2c9101d757da</t>
+    "jobId": "019daebe-4481-7062-bf05-01ad34b53c45"
+}</t>
+  </si>
+  <si>
+    <t>019daebe-4a17-719e-bb43-eb7465657884</t>
   </si>
   <si>
     <t>{
     "message": "Crawl job created successfully.",
-    "jobId": "019da9be-6063-7182-8ffe-2c9101d757da"
-}</t>
-  </si>
-  <si>
-    <t>019da9be-64c3-70f9-a26c-2bddb9beed1e</t>
+    "jobId": "019daebe-4a17-719e-bb43-eb7465657884"
+}</t>
+  </si>
+  <si>
+    <t>019daebe-4e51-7563-ac09-8c930d0822b6</t>
   </si>
   <si>
     <t>{
     "message": "Crawl job created successfully.",
-    "jobId": "019da9be-64c3-70f9-a26c-2bddb9beed1e"
-}</t>
-  </si>
-  <si>
-    <t>019da9be-6988-71b3-8368-91538e139e81</t>
+    "jobId": "019daebe-4e51-7563-ac09-8c930d0822b6"
+}</t>
+  </si>
+  <si>
+    <t>019daebe-5292-7018-b4ea-e12ee3c287c6</t>
   </si>
   <si>
     <t>{
     "message": "Crawl job created successfully.",
-    "jobId": "019da9be-6988-71b3-8368-91538e139e81"
-}</t>
-  </si>
-  <si>
-    <t>019da9be-6e3f-736c-82d2-872eb80c1057</t>
+    "jobId": "019daebe-5292-7018-b4ea-e12ee3c287c6"
+}</t>
+  </si>
+  <si>
+    <t>019daebe-56e0-7409-8f18-d5bded1bcaea</t>
   </si>
   <si>
     <t>{
     "message": "Crawl job created successfully.",
-    "jobId": "019da9be-6e3f-736c-82d2-872eb80c1057"
-}</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>{
-    "statusCode": 400,
-    "path": "/crawl/submit",
-    "message": {
-        "message": "When link discovery is off, depth must be 0. Remove \"depth\" or set it to 0.",
-        "error": "Bad Request",
-        "statusCode": 400
-    }
-}</t>
-  </si>
-  <si>
-    <t>019da9be-769b-756b-b647-619316dab1d1</t>
+    "jobId": "019daebe-56e0-7409-8f18-d5bded1bcaea"
+}</t>
+  </si>
+  <si>
+    <t>019daebe-5b0b-733c-986f-53a416932ee6</t>
   </si>
   <si>
     <t>{
     "message": "Crawl job created successfully.",
-    "jobId": "019da9be-769b-756b-b647-619316dab1d1"
-}</t>
-  </si>
-  <si>
-    <t>019da9be-7b37-744c-83e6-41e78aeb2260</t>
+    "jobId": "019daebe-5b0b-733c-986f-53a416932ee6"
+}</t>
+  </si>
+  <si>
+    <t>019daebe-5f40-765c-b59e-6445d04502e4</t>
   </si>
   <si>
     <t>{
     "message": "Crawl job created successfully.",
-    "jobId": "019da9be-7b37-744c-83e6-41e78aeb2260"
-}</t>
-  </si>
-  <si>
-    <t>019da9be-7fb0-77b8-a2ad-3a8c797e2729</t>
+    "jobId": "019daebe-5f40-765c-b59e-6445d04502e4"
+}</t>
+  </si>
+  <si>
+    <t>019daebe-6393-76ba-b044-61509753eb7d</t>
   </si>
   <si>
     <t>{
     "message": "Crawl job created successfully.",
-    "jobId": "019da9be-7fb0-77b8-a2ad-3a8c797e2729"
-}</t>
-  </si>
-  <si>
-    <t>019da9be-840e-73a5-83ee-03adaeadf46c</t>
+    "jobId": "019daebe-6393-76ba-b044-61509753eb7d"
+}</t>
+  </si>
+  <si>
+    <t>019daebe-67ca-705b-89ad-7815fcd4056e</t>
   </si>
   <si>
     <t>{
     "message": "Crawl job created successfully.",
-    "jobId": "019da9be-840e-73a5-83ee-03adaeadf46c"
-}</t>
-  </si>
-  <si>
-    <t>019da9be-88b2-72c5-9cde-1a2f5e0ebfbf</t>
+    "jobId": "019daebe-67ca-705b-89ad-7815fcd4056e"
+}</t>
+  </si>
+  <si>
+    <t>019daebe-6c0b-74dc-ac57-8529b7af78e4</t>
   </si>
   <si>
     <t>{
     "message": "Crawl job created successfully.",
-    "jobId": "019da9be-88b2-72c5-9cde-1a2f5e0ebfbf"
-}</t>
-  </si>
-  <si>
-    <t>019da9be-8d27-742e-ab68-292553fa9f6d</t>
+    "jobId": "019daebe-6c0b-74dc-ac57-8529b7af78e4"
+}</t>
+  </si>
+  <si>
+    <t>019daebe-704b-74ec-96e0-8180c1a4d576</t>
   </si>
   <si>
     <t>{
     "message": "Crawl job created successfully.",
-    "jobId": "019da9be-8d27-742e-ab68-292553fa9f6d"
-}</t>
-  </si>
-  <si>
-    <t>019da9be-91c8-705b-8f16-035f9e5893b6</t>
+    "jobId": "019daebe-704b-74ec-96e0-8180c1a4d576"
+}</t>
+  </si>
+  <si>
+    <t>019daebe-747e-72a5-95e0-a9a2f5612093</t>
   </si>
   <si>
     <t>{
     "message": "Crawl job created successfully.",
-    "jobId": "019da9be-91c8-705b-8f16-035f9e5893b6"
-}</t>
-  </si>
-  <si>
-    <t>019da9be-965b-7399-a4fa-2646bb838075</t>
+    "jobId": "019daebe-747e-72a5-95e0-a9a2f5612093"
+}</t>
+  </si>
+  <si>
+    <t>019daebe-78a9-732c-9d0f-2e4cba8f0ffb</t>
   </si>
   <si>
     <t>{
     "message": "Crawl job created successfully.",
-    "jobId": "019da9be-965b-7399-a4fa-2646bb838075"
-}</t>
-  </si>
-  <si>
-    <t>019da9be-9ade-75c9-96a6-d01287639f01</t>
+    "jobId": "019daebe-78a9-732c-9d0f-2e4cba8f0ffb"
+}</t>
+  </si>
+  <si>
+    <t>019daebe-7cf5-7419-9d77-e508b70be11c</t>
   </si>
   <si>
     <t>{
     "message": "Crawl job created successfully.",
-    "jobId": "019da9be-9ade-75c9-96a6-d01287639f01"
-}</t>
-  </si>
-  <si>
-    <t>019da9be-9f6a-7734-b557-63e9b92e7d19</t>
+    "jobId": "019daebe-7cf5-7419-9d77-e508b70be11c"
+}</t>
+  </si>
+  <si>
+    <t>019daebe-8126-714f-8f47-85ad73519db5</t>
   </si>
   <si>
     <t>{
     "message": "Crawl job created successfully.",
-    "jobId": "019da9be-9f6a-7734-b557-63e9b92e7d19"
-}</t>
-  </si>
-  <si>
-    <t>019da9be-a410-749e-ae16-ec8e8c49ed79</t>
+    "jobId": "019daebe-8126-714f-8f47-85ad73519db5"
+}</t>
+  </si>
+  <si>
+    <t>019daebe-8556-7043-bffa-1a446d4ff5f3</t>
   </si>
   <si>
     <t>{
     "message": "Crawl job created successfully.",
-    "jobId": "019da9be-a410-749e-ae16-ec8e8c49ed79"
-}</t>
-  </si>
-  <si>
-    <t>019da9be-a8f5-7709-b536-c18c4343301e</t>
+    "jobId": "019daebe-8556-7043-bffa-1a446d4ff5f3"
+}</t>
+  </si>
+  <si>
+    <t>019daebe-8986-74d7-a8af-f81cc80f70a1</t>
   </si>
   <si>
     <t>{
     "message": "Crawl job created successfully.",
-    "jobId": "019da9be-a8f5-7709-b536-c18c4343301e"
-}</t>
-  </si>
-  <si>
-    <t>019da9be-ad58-75b8-b907-7a73b29e3d86</t>
+    "jobId": "019daebe-8986-74d7-a8af-f81cc80f70a1"
+}</t>
+  </si>
+  <si>
+    <t>019daebe-8da2-745f-9b7f-71a8f2c187f8</t>
   </si>
   <si>
     <t>{
     "message": "Crawl job created successfully.",
-    "jobId": "019da9be-ad58-75b8-b907-7a73b29e3d86"
-}</t>
-  </si>
-  <si>
-    <t>019da9be-b195-70d6-85c0-4e3d897767c9</t>
+    "jobId": "019daebe-8da2-745f-9b7f-71a8f2c187f8"
+}</t>
+  </si>
+  <si>
+    <t>019daebe-91e9-7479-a0c8-2c6f03c87323</t>
   </si>
   <si>
     <t>{
     "message": "Crawl job created successfully.",
-    "jobId": "019da9be-b195-70d6-85c0-4e3d897767c9"
-}</t>
-  </si>
-  <si>
-    <t>{
-    "statusCode": 429,
-    "path": "/crawl/submit",
-    "message": "ThrottlerException: Too Many Requests"
+    "jobId": "019daebe-91e9-7479-a0c8-2c6f03c87323"
 }</t>
   </si>
   <si>
@@ -253,6 +232,685 @@
   </si>
   <si>
     <t>running</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-4481-7062-bf05-01ad34b53c45",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://m.youtube.com"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://m.youtube.com.",
+    "runtimeTaskId": "4eff75e433ce4495a0b639e0b8f7b3f6",
+    "createdAt": "2026-04-21T06:33:18.214Z",
+    "startedAt": "2026-04-21T06:57:23.852Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 10,
+    "uniqueLinks": 4,
+    "processedLinks": 4,
+    "failedLinks": 0,
+    "excludedLinks": 3,
+    "duplicateLinks": 3,
+    "depth": 1,
+    "completedAt": "2026-04-21T06:58:50.164Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-4a17-719e-bb43-eb7465657884",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://myownadvisor.ca"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://myownadvisor.ca.",
+    "runtimeTaskId": "3044d07d8bbd45d48de607da94e1be3b",
+    "createdAt": "2026-04-21T06:33:19.642Z",
+    "startedAt": "2026-04-21T07:00:30.262Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 0,
+    "uniqueLinks": 0,
+    "processedLinks": 0,
+    "failedLinks": 1,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 1,
+    "completedAt": "2026-04-21T07:01:09.221Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-4e51-7563-ac09-8c930d0822b6",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://nerdwallet.com"
+    ],
+    "status": "running",
+    "message": "Crawling process is running for https://nerdwallet.com",
+    "runtimeTaskId": "5740fb299447439aabc7e59b563bd3e4",
+    "createdAt": "2026-04-21T06:33:20.725Z",
+    "startedAt": "2026-04-21T07:02:54.505Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 451,
+    "uniqueLinks": 327,
+    "processedLinks": 177,
+    "failedLinks": 2,
+    "excludedLinks": 26,
+    "duplicateLinks": 123,
+    "depth": 1
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-5292-7018-b4ea-e12ee3c287c6",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://newsweek.com"
+    ],
+    "status": "running",
+    "message": "Crawling process is running for https://newsweek.com",
+    "runtimeTaskId": "67bd503a366e4c44b889888e1f1ec339",
+    "createdAt": "2026-04-21T06:33:21.813Z",
+    "startedAt": "2026-04-21T07:16:34.510Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 671,
+    "uniqueLinks": 175,
+    "processedLinks": 83,
+    "failedLinks": 3,
+    "excludedLinks": 20,
+    "duplicateLinks": 494,
+    "depth": 1
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-56e0-7409-8f18-d5bded1bcaea",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://offerhub.ca"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://offerhub.ca.",
+    "runtimeTaskId": "d4c6b5de30c4441eb541b4ecdd21d0e9",
+    "createdAt": "2026-04-21T06:33:22.916Z",
+    "startedAt": "2026-04-21T07:22:12.312Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 0,
+    "uniqueLinks": 0,
+    "processedLinks": 0,
+    "failedLinks": 1,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 1,
+    "completedAt": "2026-04-21T07:23:31.014Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-5b0b-733c-986f-53a416932ee6",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://planhub.ca"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://planhub.ca.",
+    "runtimeTaskId": "e9fdcc7807f2498c96ccc0e917a26968",
+    "createdAt": "2026-04-21T06:33:23.982Z",
+    "startedAt": "2026-04-21T07:24:59.954Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 0,
+    "uniqueLinks": 0,
+    "processedLinks": 0,
+    "failedLinks": 1,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 1,
+    "completedAt": "2026-04-21T07:26:30.673Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-5f40-765c-b59e-6445d04502e4",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://rebatesme.com"
+    ],
+    "status": "running",
+    "message": "Crawling process is running for https://rebatesme.com",
+    "runtimeTaskId": "645f9a097d84489199046879d3820599",
+    "createdAt": "2026-04-21T06:33:25.060Z",
+    "startedAt": "2026-04-21T07:28:11.494Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 142,
+    "uniqueLinks": 96,
+    "processedLinks": 75,
+    "failedLinks": 4,
+    "excludedLinks": 17,
+    "duplicateLinks": 43,
+    "depth": 1
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-6393-76ba-b044-61509753eb7d",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://redflagdeals.com"
+    ],
+    "status": "running",
+    "message": "Crawling process is running for https://redflagdeals.com",
+    "runtimeTaskId": "68a3737c3079493fa4497b877d4f2564",
+    "createdAt": "2026-04-21T06:33:26.167Z",
+    "startedAt": "2026-04-21T07:30:41.170Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 432,
+    "uniqueLinks": 283,
+    "processedLinks": 40,
+    "failedLinks": 3,
+    "excludedLinks": 58,
+    "duplicateLinks": 142,
+    "depth": 1
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-67ca-705b-89ad-7815fcd4056e",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://retirehappy.ca"
+    ],
+    "status": "running",
+    "message": "Crawling process is running for https://retirehappy.ca",
+    "runtimeTaskId": "447debc5f2834edd94ffdbbb4281451e",
+    "createdAt": "2026-04-21T06:33:27.245Z",
+    "startedAt": "2026-04-21T07:38:36.993Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 90,
+    "uniqueLinks": 70,
+    "processedLinks": 45,
+    "failedLinks": 0,
+    "excludedLinks": 19,
+    "duplicateLinks": 18,
+    "depth": 1
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-6c0b-74dc-ac57-8529b7af78e4",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://simplerate.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://simplerate.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-704b-74ec-96e0-8180c1a4d576",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://smartmoneyhabits.com"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://smartmoneyhabits.com"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-747e-72a5-95e0-a9a2f5612093",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://smartwealthfinancial.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://smartwealthfinancial.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-78a9-732c-9d0f-2e4cba8f0ffb",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://stockscanada.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://stockscanada.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-7cf5-7419-9d77-e508b70be11c",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://tangerine.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://tangerine.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-8126-714f-8f47-85ad73519db5",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://thechexyrundown.beehiiv.com"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://thechexyrundown.beehiiv.com"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-8556-7043-bffa-1a446d4ff5f3",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://theinformr.com"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://theinformr.com"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-8986-74d7-a8af-f81cc80f70a1",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://thestar.com"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://thestar.com"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-8da2-745f-9b7f-71a8f2c187f8",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://theverge.com"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://theverge.com"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-91e9-7479-a0c8-2c6f03c87323",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://time.com"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://time.com"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-4e51-7563-ac09-8c930d0822b6",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://nerdwallet.com"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://nerdwallet.com.",
+    "runtimeTaskId": "5740fb299447439aabc7e59b563bd3e4",
+    "createdAt": "2026-04-21T06:33:20.725Z",
+    "startedAt": "2026-04-21T07:02:54.505Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 451,
+    "uniqueLinks": 327,
+    "processedLinks": 274,
+    "failedLinks": 28,
+    "excludedLinks": 26,
+    "duplicateLinks": 123,
+    "depth": 1,
+    "completedAt": "2026-04-21T08:41:46.575Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-5292-7018-b4ea-e12ee3c287c6",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://newsweek.com"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://newsweek.com.",
+    "runtimeTaskId": "67bd503a366e4c44b889888e1f1ec339",
+    "createdAt": "2026-04-21T06:33:21.813Z",
+    "startedAt": "2026-04-21T07:16:34.510Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 671,
+    "uniqueLinks": 175,
+    "processedLinks": 154,
+    "failedLinks": 3,
+    "excludedLinks": 20,
+    "duplicateLinks": 494,
+    "depth": 1,
+    "completedAt": "2026-04-21T08:13:29.289Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-5f40-765c-b59e-6445d04502e4",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://rebatesme.com"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://rebatesme.com.",
+    "runtimeTaskId": "645f9a097d84489199046879d3820599",
+    "createdAt": "2026-04-21T06:33:25.060Z",
+    "startedAt": "2026-04-21T07:28:11.494Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 142,
+    "uniqueLinks": 96,
+    "processedLinks": 78,
+    "failedLinks": 4,
+    "excludedLinks": 17,
+    "duplicateLinks": 43,
+    "depth": 1,
+    "completedAt": "2026-04-21T07:51:37.784Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-6393-76ba-b044-61509753eb7d",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://redflagdeals.com"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://redflagdeals.com.",
+    "runtimeTaskId": "68a3737c3079493fa4497b877d4f2564",
+    "createdAt": "2026-04-21T06:33:26.167Z",
+    "startedAt": "2026-04-21T07:30:41.170Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 432,
+    "uniqueLinks": 283,
+    "processedLinks": 227,
+    "failedLinks": 5,
+    "excludedLinks": 58,
+    "duplicateLinks": 142,
+    "depth": 1,
+    "completedAt": "2026-04-21T09:09:18.982Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-67ca-705b-89ad-7815fcd4056e",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://retirehappy.ca"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://retirehappy.ca.",
+    "runtimeTaskId": "447debc5f2834edd94ffdbbb4281451e",
+    "createdAt": "2026-04-21T06:33:27.245Z",
+    "startedAt": "2026-04-21T07:38:36.993Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 90,
+    "uniqueLinks": 70,
+    "processedLinks": 53,
+    "failedLinks": 0,
+    "excludedLinks": 19,
+    "duplicateLinks": 18,
+    "depth": 1,
+    "completedAt": "2026-04-21T07:52:57.328Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-6c0b-74dc-ac57-8529b7af78e4",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://simplerate.ca"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://simplerate.ca.",
+    "runtimeTaskId": "569807488e834907944a1fec71da4937",
+    "createdAt": "2026-04-21T06:33:28.334Z",
+    "startedAt": "2026-04-21T07:53:03.778Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 0,
+    "uniqueLinks": 0,
+    "processedLinks": 0,
+    "failedLinks": 1,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 1,
+    "completedAt": "2026-04-21T07:53:40.787Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-704b-74ec-96e0-8180c1a4d576",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://smartmoneyhabits.com"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://smartmoneyhabits.com.",
+    "runtimeTaskId": "e2624084027b49f2b2722425ec42970e",
+    "createdAt": "2026-04-21T06:33:29.422Z",
+    "startedAt": "2026-04-21T07:54:41.503Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 300,
+    "uniqueLinks": 111,
+    "processedLinks": 107,
+    "failedLinks": 0,
+    "excludedLinks": 7,
+    "duplicateLinks": 186,
+    "depth": 1,
+    "completedAt": "2026-04-21T08:16:50.758Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-747e-72a5-95e0-a9a2f5612093",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://smartwealthfinancial.ca"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://smartwealthfinancial.ca.",
+    "runtimeTaskId": "4fbdec2950e343728f142ed358fbc8f7",
+    "createdAt": "2026-04-21T06:33:30.497Z",
+    "startedAt": "2026-04-21T07:55:05.821Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 0,
+    "uniqueLinks": 0,
+    "processedLinks": 0,
+    "failedLinks": 1,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 1,
+    "completedAt": "2026-04-21T07:55:44.019Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-78a9-732c-9d0f-2e4cba8f0ffb",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://stockscanada.ca"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://stockscanada.ca.",
+    "runtimeTaskId": "a3af832fe9a44d91850a3917566e7b7a",
+    "createdAt": "2026-04-21T06:33:31.564Z",
+    "startedAt": "2026-04-21T07:57:22.602Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 137,
+    "uniqueLinks": 57,
+    "processedLinks": 49,
+    "failedLinks": 0,
+    "excludedLinks": 27,
+    "duplicateLinks": 61,
+    "depth": 1,
+    "completedAt": "2026-04-21T08:09:21.196Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-7cf5-7419-9d77-e508b70be11c",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://tangerine.ca"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://tangerine.ca.",
+    "runtimeTaskId": "061a95e05c95467382c817b4d80bfcf7",
+    "createdAt": "2026-04-21T06:33:32.664Z",
+    "startedAt": "2026-04-21T08:00:12.495Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 223,
+    "uniqueLinks": 96,
+    "processedLinks": 82,
+    "failedLinks": 0,
+    "excludedLinks": 19,
+    "duplicateLinks": 122,
+    "depth": 1,
+    "completedAt": "2026-04-21T08:17:35.772Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-8126-714f-8f47-85ad73519db5",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://thechexyrundown.beehiiv.com"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://thechexyrundown.beehiiv.com.",
+    "runtimeTaskId": "a4ca4b3fe3684744ab6add4af3ca055d",
+    "createdAt": "2026-04-21T06:33:33.737Z",
+    "startedAt": "2026-04-21T08:03:48.944Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 74,
+    "uniqueLinks": 32,
+    "processedLinks": 27,
+    "failedLinks": 1,
+    "excludedLinks": 4,
+    "duplicateLinks": 42,
+    "depth": 1,
+    "completedAt": "2026-04-21T08:13:51.856Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-8556-7043-bffa-1a446d4ff5f3",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://theinformr.com"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://theinformr.com.",
+    "runtimeTaskId": "ff1c720f72694f4a9ea25985ac740483",
+    "createdAt": "2026-04-21T06:33:34.809Z",
+    "startedAt": "2026-04-21T08:10:26.601Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 0,
+    "uniqueLinks": 0,
+    "processedLinks": 0,
+    "failedLinks": 1,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 1,
+    "completedAt": "2026-04-21T08:11:58.112Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-8986-74d7-a8af-f81cc80f70a1",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://thestar.com"
+    ],
+    "status": "running",
+    "message": "Crawling process is running for https://thestar.com",
+    "runtimeTaskId": "60a5300c8017400c90637fc714685f46",
+    "createdAt": "2026-04-21T06:33:35.882Z",
+    "startedAt": "2026-04-21T08:11:01.582Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 573,
+    "uniqueLinks": 223,
+    "processedLinks": 138,
+    "failedLinks": 17,
+    "excludedLinks": 47,
+    "duplicateLinks": 333,
+    "depth": 1
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-8da2-745f-9b7f-71a8f2c187f8",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://theverge.com"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://theverge.com.",
+    "runtimeTaskId": "6003821f2f394a1c8f91f83e51ae2bfc",
+    "createdAt": "2026-04-21T06:33:36.934Z",
+    "startedAt": "2026-04-21T08:13:42.364Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 365,
+    "uniqueLinks": 197,
+    "processedLinks": 157,
+    "failedLinks": 5,
+    "excludedLinks": 38,
+    "duplicateLinks": 165,
+    "depth": 1,
+    "completedAt": "2026-04-21T09:08:55.434Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-91e9-7479-a0c8-2c6f03c87323",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://time.com"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://time.com.",
+    "runtimeTaskId": "279a3ebb42164f47b9b0cddf7b799422",
+    "createdAt": "2026-04-21T06:33:38.029Z",
+    "startedAt": "2026-04-21T08:15:13.933Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 201,
+    "uniqueLinks": 99,
+    "processedLinks": 86,
+    "failedLinks": 2,
+    "excludedLinks": 15,
+    "duplicateLinks": 98,
+    "depth": 1,
+    "completedAt": "2026-04-21T08:42:35.165Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019daebe-8986-74d7-a8af-f81cc80f70a1",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://thestar.com"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://thestar.com.",
+    "runtimeTaskId": "60a5300c8017400c90637fc714685f46",
+    "createdAt": "2026-04-21T06:33:35.882Z",
+    "startedAt": "2026-04-21T08:11:01.582Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 573,
+    "uniqueLinks": 223,
+    "processedLinks": 173,
+    "failedLinks": 20,
+    "excludedLinks": 47,
+    "duplicateLinks": 333,
+    "depth": 1,
+    "completedAt": "2026-04-21T09:29:35.390Z"
+}</t>
   </si>
 </sst>
 </file>
@@ -625,7 +1283,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95DF0F3A-A575-4E1C-BD31-366F2E5919E5}">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="37.5546875"/>
@@ -700,7 +1358,7 @@
         <v>12</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>400.0</v>
+        <v>201.0</v>
       </c>
       <c r="C7" t="s" s="0">
         <v>13</v>
@@ -847,39 +1505,6 @@
       </c>
       <c r="C20" t="s" s="0">
         <v>39</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="B21" t="n" s="0">
-        <v>201.0</v>
-      </c>
-      <c r="C21" t="s" s="0">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="B22" t="n" s="0">
-        <v>429.0</v>
-      </c>
-      <c r="C22" t="s" s="0">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="B23" t="n" s="0">
-        <v>429.0</v>
-      </c>
-      <c r="C23" t="s" s="0">
-        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -890,18 +1515,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>45</v>
+        <v>42</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="2">
@@ -909,10 +1537,13 @@
         <v>2</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>200.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>46</v>
       </c>
     </row>
     <row r="3">
@@ -920,10 +1551,13 @@
         <v>4</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>200.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>47</v>
       </c>
     </row>
     <row r="4">
@@ -931,10 +1565,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>200.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>65</v>
       </c>
     </row>
     <row r="5">
@@ -942,10 +1579,13 @@
         <v>8</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>200.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>66</v>
       </c>
     </row>
     <row r="6">
@@ -953,164 +1593,209 @@
         <v>10</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>200.0</v>
       </c>
+      <c r="D6" t="s" s="0">
+        <v>50</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>200.0</v>
       </c>
+      <c r="D7" t="s" s="0">
+        <v>51</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>200.0</v>
       </c>
+      <c r="D8" t="s" s="0">
+        <v>67</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n" s="0">
         <v>200.0</v>
       </c>
+      <c r="D9" t="s" s="0">
+        <v>68</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>200.0</v>
       </c>
+      <c r="D10" t="s" s="0">
+        <v>69</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>200.0</v>
       </c>
+      <c r="D11" t="s" s="0">
+        <v>70</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>200.0</v>
       </c>
+      <c r="D12" t="s" s="0">
+        <v>71</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C13" t="n" s="0">
         <v>200.0</v>
       </c>
+      <c r="D13" t="s" s="0">
+        <v>72</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C14" t="n" s="0">
         <v>200.0</v>
       </c>
+      <c r="D14" t="s" s="0">
+        <v>73</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C15" t="n" s="0">
         <v>200.0</v>
       </c>
+      <c r="D15" t="s" s="0">
+        <v>74</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>200.0</v>
       </c>
+      <c r="D16" t="s" s="0">
+        <v>75</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>200.0</v>
       </c>
+      <c r="D17" t="s" s="0">
+        <v>76</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C18" t="n" s="0">
         <v>200.0</v>
       </c>
+      <c r="D18" t="s" s="0">
+        <v>80</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C19" t="n" s="0">
         <v>200.0</v>
       </c>
+      <c r="D19" t="s" s="0">
+        <v>78</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C20" t="n" s="0">
         <v>200.0</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/response.xlsx
+++ b/src/test/resources/response.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="335">
   <si>
     <t>Response</t>
   </si>
@@ -454,6 +454,3210 @@
     ],
     "status": "queued",
     "message": "Crawling process is queued for https://crawldemolinksnew.signitydemo.in"
+}</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-51f6-70f1-948b-5ff8f9b2af4f",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://en.wikipedia.org/wiki/Category:Machine_learning_algorithms"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://en.wikipedia.org/wiki/Category:Machine_learning_algorithms.",
+    "runtimeTaskId": "843ba20b346e484797695373f854c26c",
+    "createdAt": "2026-04-30T07:47:22.745Z",
+    "startedAt": "2026-05-01T01:16:14.865Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-01T01:16:29.242Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-578c-734b-84cf-2030acc3c26c",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://en.wikipedia.org/wiki/Category:Artificial_intelligence"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://en.wikipedia.org/wiki/Category:Artificial_intelligence.",
+    "runtimeTaskId": "b470c07df37a4ade805a6e0e81c2982d",
+    "createdAt": "2026-04-30T07:47:24.175Z",
+    "startedAt": "2026-05-01T01:17:50.932Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-01T01:18:05.143Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-5bdb-70fa-9d0f-230890e4485d",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://en.wikipedia.org/wiki/Special:Search?search=Machine%20Learning"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://en.wikipedia.org/wiki/Special:Search?search=Machine%20Learning.",
+    "runtimeTaskId": "ce8e85524ef140b4b31fe60be0381b19",
+    "createdAt": "2026-04-30T07:47:25.277Z",
+    "startedAt": "2026-05-01T01:18:28.264Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-01T01:18:55.331Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-5ff2-763d-9bba-0751e3a5ceec",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://en.wikipedia.org/w/index.php?search=Research&amp;title=Special:Search"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://en.wikipedia.org/w/index.php?search=Research&amp;title=Special:Search.",
+    "runtimeTaskId": "6a452baeda80458e9a6c81c513e00451",
+    "createdAt": "2026-04-30T07:47:26.324Z",
+    "startedAt": "2026-05-01T01:19:47.967Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-01T01:20:25.538Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-642b-736d-91b8-65d85b6310ec",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://en.wikipedia.org/w/index.php?search=Java_(programming_language)&amp;title=Special:Search"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://en.wikipedia.org/w/index.php?search=Java_(programming_language)&amp;title=Special:Search.",
+    "runtimeTaskId": "2f72d1df9c7146c1811cb73fe1bcf179",
+    "createdAt": "2026-04-30T07:47:27.405Z",
+    "startedAt": "2026-05-01T01:19:55.121Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-01T01:20:16.922Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-6842-75eb-b48e-74be2784511c",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "HTTP://EXAMPL.COM:80/"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for HTTP://EXAMPL.COM:80/.",
+    "runtimeTaskId": "e181ab25d5534c818a9b2abb9498b37a",
+    "createdAt": "2026-04-30T07:47:28.453Z",
+    "startedAt": "2026-05-01T01:20:28.604Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 0,
+    "failedLinks": 1,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-01T01:21:28.882Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-6c49-7341-9363-423c6ce55e0a",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://en.wikipedia.org/wiki/C%2B%2B"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://en.wikipedia.org/wiki/C%2B%2B.",
+    "runtimeTaskId": "a4b8dbffd1814b1c8e25cc2b6d3e89d6",
+    "createdAt": "2026-04-30T07:47:29.483Z",
+    "startedAt": "2026-05-01T01:20:37.430Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-01T01:20:57.549Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-703b-7478-8766-570ec3638bbe",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://en.wikipedia.org/w/index.php?search=machine+learning"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://en.wikipedia.org/w/index.php?search=machine+learning.",
+    "runtimeTaskId": "ee16d4fb2cf54e90acd9cece62270e46",
+    "createdAt": "2026-04-30T07:47:30.492Z",
+    "startedAt": "2026-05-01T01:21:49.128Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-01T01:22:10.902Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-7450-74cd-84fa-98cdaf478e29",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://a.com?b=2&amp;a=1"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://a.com?b=2&amp;a=1.",
+    "runtimeTaskId": "d7b95b8fd894457faa72b8d4eb32163f",
+    "createdAt": "2026-04-30T07:47:31.538Z",
+    "startedAt": "2026-05-01T01:22:21.066Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 0,
+    "failedLinks": 1,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-01T01:22:59.337Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-7852-7258-bd79-ecd3dc6d03bb",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://www.save.ca/flyers/"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://www.save.ca/flyers/.",
+    "runtimeTaskId": "d231d86e4d404eebac1e7babfc641373",
+    "createdAt": "2026-04-30T07:47:32.563Z",
+    "startedAt": "2026-05-01T01:23:00.804Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-01T01:23:25.857Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-7cca-7679-a370-5eae09feddc2",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://www.buzzfeed.com/ca"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://www.buzzfeed.com/ca.",
+    "runtimeTaskId": "074ad49980fe4da78387d9e3248c3eb7",
+    "createdAt": "2026-04-30T07:47:33.708Z",
+    "startedAt": "2026-05-01T04:49:41.452Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 350,
+    "uniqueLinks": 287,
+    "processedLinks": 273,
+    "failedLinks": 1,
+    "excludedLinks": 14,
+    "duplicateLinks": 62,
+    "depth": 1,
+    "completedAt": "2026-05-01T07:03:17.618Z"
+}</t>
+  </si>
+  <si>
+    <t>running</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-80d9-7056-8718-af96cd1a75d6",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://globo.com"
+    ],
+    "status": "running",
+    "message": "Crawling process is running for https://globo.com",
+    "runtimeTaskId": "b472df5dd44c4e3eb50a8f5e42efde4f",
+    "createdAt": "2026-04-30T07:47:34.747Z",
+    "startedAt": "2026-05-01T04:49:56.784Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 605,
+    "uniqueLinks": 457,
+    "processedLinks": 270,
+    "failedLinks": 9,
+    "excludedLinks": 61,
+    "duplicateLinks": 146,
+    "depth": 1
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-8501-7620-9ac3-1cbd721ab356",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://www.hsbc.com/"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://www.hsbc.com/.",
+    "runtimeTaskId": "91d88b04b0a346669b588569064f5701",
+    "createdAt": "2026-04-30T07:47:35.810Z",
+    "startedAt": "2026-05-01T05:00:50.577Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 224,
+    "uniqueLinks": 134,
+    "processedLinks": 19,
+    "failedLinks": 104,
+    "excludedLinks": 14,
+    "duplicateLinks": 87,
+    "depth": 1,
+    "completedAt": "2026-05-01T05:33:07.068Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-892e-7604-8f79-92277ba55266",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://theinformr.com"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://theinformr.com.",
+    "runtimeTaskId": "c48bc67b037c4f17b33c62171829a539",
+    "createdAt": "2026-04-30T07:47:36.879Z",
+    "startedAt": "2026-05-01T05:01:48.286Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 0,
+    "uniqueLinks": 0,
+    "processedLinks": 0,
+    "failedLinks": 1,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 1,
+    "completedAt": "2026-05-01T05:03:16.874Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-8d37-74a9-9161-b609b6f2100d",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://simplerate.ca"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://simplerate.ca.",
+    "runtimeTaskId": "ff201e0b0ff6409fb8c94358f7849e67",
+    "createdAt": "2026-04-30T07:47:37.912Z",
+    "startedAt": "2026-05-01T05:04:17.615Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 0,
+    "uniqueLinks": 0,
+    "processedLinks": 0,
+    "failedLinks": 1,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 1,
+    "completedAt": "2026-05-01T05:04:56.814Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-915e-75eb-83c8-b4029284ce31",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://atila.ca"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://atila.ca.",
+    "runtimeTaskId": "6f2d87043b804457a54027e7f233a919",
+    "createdAt": "2026-04-30T07:47:38.976Z",
+    "startedAt": "2026-05-01T05:04:51.274Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 128,
+    "uniqueLinks": 71,
+    "processedLinks": 52,
+    "failedLinks": 2,
+    "excludedLinks": 18,
+    "duplicateLinks": 56,
+    "depth": 1,
+    "completedAt": "2026-05-01T05:10:35.378Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-957a-721f-a17d-6654db9c1575",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://apnews.com/"
+    ],
+    "status": "running",
+    "message": "Crawling process is running for https://apnews.com/",
+    "runtimeTaskId": "d3c2c3d7901d4e84b4c516b2c1f7e53d",
+    "createdAt": "2026-04-30T07:47:40.028Z",
+    "startedAt": "2026-05-01T05:06:24.453Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 1564,
+    "uniqueLinks": 294,
+    "processedLinks": 200,
+    "failedLinks": 0,
+    "excludedLinks": 40,
+    "duplicateLinks": 1268,
+    "depth": 1
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-9986-740c-9dbb-95c33c94a5a6",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://moneyeh.ca/"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://moneyeh.ca/.",
+    "runtimeTaskId": "8ca4da9f27884833ae7c7711a1be0887",
+    "createdAt": "2026-04-30T07:47:41.064Z",
+    "startedAt": "2026-05-01T05:12:03.876Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 84,
+    "uniqueLinks": 54,
+    "processedLinks": 52,
+    "failedLinks": 0,
+    "excludedLinks": 2,
+    "duplicateLinks": 30,
+    "depth": 1,
+    "completedAt": "2026-05-01T05:16:15.506Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-9d7d-70e9-b3c8-7e816c78b548",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://www.buzzfeed.com/ca"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://www.buzzfeed.com/ca.",
+    "runtimeTaskId": "21321416688447c3a8b16c4d724b8221",
+    "createdAt": "2026-04-30T07:47:42.078Z",
+    "startedAt": "2026-05-01T05:17:35.635Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 351,
+    "uniqueLinks": 288,
+    "processedLinks": 273,
+    "failedLinks": 1,
+    "excludedLinks": 15,
+    "duplicateLinks": 62,
+    "depth": 1,
+    "completedAt": "2026-05-01T07:07:09.482Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-a165-7538-bce5-13a3edaea1d2",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://crawldemolinksnew.signitydemo.in"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://crawldemolinksnew.signitydemo.in.",
+    "runtimeTaskId": "cd928e0a7e2c41f68d837ea90531df4d",
+    "createdAt": "2026-04-30T07:47:43.079Z",
+    "startedAt": "2026-05-01T05:29:51.062Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 0,
+    "uniqueLinks": 0,
+    "processedLinks": 0,
+    "failedLinks": 1,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 1,
+    "completedAt": "2026-05-01T05:35:33.606Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-51f6-70f1-948b-5ff8f9b2af4f",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://en.wikipedia.org/wiki/Category:Machine_learning_algorithms"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://en.wikipedia.org/wiki/Category:Machine_learning_algorithms.",
+    "runtimeTaskId": "ff501034946843c08fa7d3e2b8124150",
+    "createdAt": "2026-04-30T07:47:22.745Z",
+    "startedAt": "2026-05-05T02:05:51.568Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-05T02:06:04.464Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-578c-734b-84cf-2030acc3c26c",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://en.wikipedia.org/wiki/Category:Artificial_intelligence"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://en.wikipedia.org/wiki/Category:Artificial_intelligence.",
+    "runtimeTaskId": "60ea9338f1b04d5aad63a8bd3cf44ff2",
+    "createdAt": "2026-04-30T07:47:24.175Z",
+    "startedAt": "2026-05-05T02:06:57.358Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-05T02:07:18.483Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-5bdb-70fa-9d0f-230890e4485d",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://en.wikipedia.org/wiki/Special:Search?search=Machine%20Learning"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://en.wikipedia.org/wiki/Special:Search?search=Machine%20Learning.",
+    "runtimeTaskId": "7eeebb6842004483b4c7d5db26d98736",
+    "createdAt": "2026-04-30T07:47:25.277Z",
+    "startedAt": "2026-05-05T02:07:08.767Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-05T02:07:31.217Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-5ff2-763d-9bba-0751e3a5ceec",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://en.wikipedia.org/w/index.php?search=Research&amp;title=Special:Search"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://en.wikipedia.org/w/index.php?search=Research&amp;title=Special:Search.",
+    "runtimeTaskId": "43851f451a454ea69393ca146f82ba6d",
+    "createdAt": "2026-04-30T07:47:26.324Z",
+    "startedAt": "2026-05-05T02:07:18.642Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-05T02:07:36.467Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-642b-736d-91b8-65d85b6310ec",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://en.wikipedia.org/w/index.php?search=Java_(programming_language)&amp;title=Special:Search"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://en.wikipedia.org/w/index.php?search=Java_(programming_language)&amp;title=Special:Search.",
+    "runtimeTaskId": "9d1d923fc5bf4226a677f0f684ebb090",
+    "createdAt": "2026-04-30T07:47:27.405Z",
+    "startedAt": "2026-05-05T02:07:40.795Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-05T02:08:01.793Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-6842-75eb-b48e-74be2784511c",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "HTTP://EXAMPL.COM:80/"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for HTTP://EXAMPL.COM:80/.",
+    "runtimeTaskId": "58bde98d38644e06865309bbcca68c09",
+    "createdAt": "2026-04-30T07:47:28.453Z",
+    "startedAt": "2026-05-05T02:08:43.721Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-05T02:09:17.017Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-6c49-7341-9363-423c6ce55e0a",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://en.wikipedia.org/wiki/C%2B%2B"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://en.wikipedia.org/wiki/C%2B%2B.",
+    "runtimeTaskId": "39facc9ff0e04347a6eebb8c36c43707",
+    "createdAt": "2026-04-30T07:47:29.483Z",
+    "startedAt": "2026-05-05T02:09:08.942Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-05T02:09:29.812Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-703b-7478-8766-570ec3638bbe",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://en.wikipedia.org/w/index.php?search=machine+learning"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://en.wikipedia.org/w/index.php?search=machine+learning.",
+    "runtimeTaskId": "897088232de64544b359ea678316c4c4",
+    "createdAt": "2026-04-30T07:47:30.492Z",
+    "startedAt": "2026-05-05T02:09:31.439Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-05T02:10:02.152Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-7450-74cd-84fa-98cdaf478e29",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://a.com?b=2&amp;a=1"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://a.com?b=2&amp;a=1.",
+    "runtimeTaskId": "6c9e665ace2f4d5ab5417925a78e56fd",
+    "createdAt": "2026-04-30T07:47:31.538Z",
+    "startedAt": "2026-05-05T02:09:59.196Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 0,
+    "failedLinks": 1,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-05T02:10:44.668Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-7852-7258-bd79-ecd3dc6d03bb",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://www.save.ca/flyers/"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://www.save.ca/flyers/.",
+    "runtimeTaskId": "22bec1bd07b8498d8a93bff96b1de9ef",
+    "createdAt": "2026-04-30T07:47:32.563Z",
+    "startedAt": "2026-05-05T02:11:02.056Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-05T02:11:20.802Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-7cca-7679-a370-5eae09feddc2",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://www.buzzfeed.com/ca"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://www.buzzfeed.com/ca.",
+    "runtimeTaskId": "15a1c24106bb4914bc60d6be458b26ef",
+    "createdAt": "2026-04-30T07:47:33.708Z",
+    "startedAt": "2026-05-05T04:21:47.373Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 349,
+    "uniqueLinks": 281,
+    "processedLinks": 1,
+    "failedLinks": 1,
+    "excludedLinks": 13,
+    "duplicateLinks": 334,
+    "depth": 1,
+    "completedAt": "2026-05-05T05:12:01.451Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-80d9-7056-8718-af96cd1a75d6",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://globo.com"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://globo.com.",
+    "runtimeTaskId": "8444f1b5deb44d66ad8199fe2b85a635",
+    "createdAt": "2026-04-30T07:47:34.747Z",
+    "startedAt": "2026-05-05T04:22:34.086Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 606,
+    "uniqueLinks": 462,
+    "processedLinks": 236,
+    "failedLinks": 5,
+    "excludedLinks": 61,
+    "duplicateLinks": 304,
+    "depth": 1,
+    "completedAt": "2026-05-05T07:18:54.440Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-8501-7620-9ac3-1cbd721ab356",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://www.hsbc.com/"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://www.hsbc.com/.",
+    "runtimeTaskId": "4d422035b54341f7a0f6744852387123",
+    "createdAt": "2026-04-30T07:47:35.810Z",
+    "startedAt": "2026-05-05T04:27:42.615Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 207,
+    "uniqueLinks": 128,
+    "processedLinks": 11,
+    "failedLinks": 10,
+    "excludedLinks": 9,
+    "duplicateLinks": 177,
+    "depth": 1,
+    "completedAt": "2026-05-05T05:18:29.584Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-892e-7604-8f79-92277ba55266",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://theinformr.com"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://theinformr.com.",
+    "runtimeTaskId": "9e698afb13f34d4783e9a1eae2a14e7e",
+    "createdAt": "2026-04-30T07:47:36.879Z",
+    "startedAt": "2026-05-05T04:36:27.546Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 0,
+    "uniqueLinks": 0,
+    "processedLinks": 0,
+    "failedLinks": 1,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 1,
+    "completedAt": "2026-05-05T04:37:22.284Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-8d37-74a9-9161-b609b6f2100d",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://simplerate.ca"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://simplerate.ca.",
+    "runtimeTaskId": "f0eadad9066b4750bebdbd77f79b2bc2",
+    "createdAt": "2026-04-30T07:47:37.912Z",
+    "startedAt": "2026-05-05T04:38:46.360Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 0,
+    "uniqueLinks": 0,
+    "processedLinks": 0,
+    "failedLinks": 1,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 1,
+    "completedAt": "2026-05-05T04:39:25.117Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-915e-75eb-83c8-b4029284ce31",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://atila.ca"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://atila.ca.",
+    "runtimeTaskId": "44d0834930ef48fe95c9f386d0438bf0",
+    "createdAt": "2026-04-30T07:47:38.976Z",
+    "startedAt": "2026-05-05T04:41:07.884Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 128,
+    "uniqueLinks": 72,
+    "processedLinks": 52,
+    "failedLinks": 2,
+    "excludedLinks": 18,
+    "duplicateLinks": 55,
+    "depth": 1,
+    "completedAt": "2026-05-05T04:46:49.833Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-957a-721f-a17d-6654db9c1575",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://apnews.com/"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://apnews.com/.",
+    "runtimeTaskId": "9ee8aeaf42d142548c1a0edbd3278705",
+    "createdAt": "2026-04-30T07:47:40.028Z",
+    "startedAt": "2026-05-05T04:48:10.381Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 1580,
+    "uniqueLinks": 289,
+    "processedLinks": 237,
+    "failedLinks": 3,
+    "excludedLinks": 41,
+    "duplicateLinks": 1298,
+    "depth": 1,
+    "completedAt": "2026-05-05T07:09:54.571Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-9986-740c-9dbb-95c33c94a5a6",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://moneyeh.ca/"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://moneyeh.ca/.",
+    "runtimeTaskId": "3faa3ddffe434a23b06619808f7d6926",
+    "createdAt": "2026-04-30T07:47:41.064Z",
+    "startedAt": "2026-05-05T05:09:09.300Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 84,
+    "uniqueLinks": 55,
+    "processedLinks": 0,
+    "failedLinks": 0,
+    "excludedLinks": 2,
+    "duplicateLinks": 81,
+    "depth": 1,
+    "completedAt": "2026-05-05T05:12:17.432Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-9d7d-70e9-b3c8-7e816c78b548",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://www.buzzfeed.com/ca"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://www.buzzfeed.com/ca.",
+    "runtimeTaskId": "31e5a362b59f4577b4ad9c761d297811",
+    "createdAt": "2026-04-30T07:47:42.078Z",
+    "startedAt": "2026-05-05T05:13:49.584Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 349,
+    "uniqueLinks": 279,
+    "processedLinks": 1,
+    "failedLinks": 1,
+    "excludedLinks": 13,
+    "duplicateLinks": 334,
+    "depth": 1,
+    "completedAt": "2026-05-05T06:09:27.580Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-a165-7538-bce5-13a3edaea1d2",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://crawldemolinksnew.signitydemo.in"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://crawldemolinksnew.signitydemo.in.",
+    "runtimeTaskId": "3de6b8ea50ec421381daece96bd72506",
+    "createdAt": "2026-04-30T07:47:43.079Z",
+    "startedAt": "2026-05-05T05:14:00.716Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 14,
+    "uniqueLinks": 10,
+    "processedLinks": 3,
+    "failedLinks": 2,
+    "excludedLinks": 6,
+    "duplicateLinks": 3,
+    "depth": 1,
+    "completedAt": "2026-05-05T05:15:19.496Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-51f6-70f1-948b-5ff8f9b2af4f",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://en.wikipedia.org/wiki/Category:Machine_learning_algorithms"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://en.wikipedia.org/wiki/Category:Machine_learning_algorithms.",
+    "runtimeTaskId": "11c5aa73e18d44bbb026bc156deb30da",
+    "createdAt": "2026-04-30T07:47:22.745Z",
+    "startedAt": "2026-05-08T01:01:55.169Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-08T01:02:08.428Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-578c-734b-84cf-2030acc3c26c",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://en.wikipedia.org/wiki/Category:Artificial_intelligence"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://en.wikipedia.org/wiki/Category:Artificial_intelligence.",
+    "runtimeTaskId": "2351fc7680044376b340ca5f7ea9420f",
+    "createdAt": "2026-04-30T07:47:24.175Z",
+    "startedAt": "2026-05-08T01:02:17.558Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-08T01:02:30.654Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-5bdb-70fa-9d0f-230890e4485d",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://en.wikipedia.org/wiki/Special:Search?search=Machine%20Learning"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://en.wikipedia.org/wiki/Special:Search?search=Machine%20Learning.",
+    "runtimeTaskId": "83d250acfb274978b1b848c849250a66",
+    "createdAt": "2026-04-30T07:47:25.277Z",
+    "startedAt": "2026-05-08T01:01:59.634Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-08T01:02:26.397Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-5ff2-763d-9bba-0751e3a5ceec",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://en.wikipedia.org/w/index.php?search=Research&amp;title=Special:Search"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://en.wikipedia.org/w/index.php?search=Research&amp;title=Special:Search.",
+    "runtimeTaskId": "3a914e5d6d004af8b7876a58f704a726",
+    "createdAt": "2026-04-30T07:47:26.324Z",
+    "startedAt": "2026-05-08T01:02:44.613Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-08T01:03:05.588Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-642b-736d-91b8-65d85b6310ec",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://en.wikipedia.org/w/index.php?search=Java_(programming_language)&amp;title=Special:Search"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://en.wikipedia.org/w/index.php?search=Java_(programming_language)&amp;title=Special:Search.",
+    "runtimeTaskId": "808cea490304427ba960a85896db36f6",
+    "createdAt": "2026-04-30T07:47:27.405Z",
+    "startedAt": "2026-05-08T01:03:02.739Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-08T01:03:39.549Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-6842-75eb-b48e-74be2784511c",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "HTTP://EXAMPL.COM:80/"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for HTTP://EXAMPL.COM:80/.",
+    "runtimeTaskId": "d79fa65316b24ddd939526786dda437e",
+    "createdAt": "2026-04-30T07:47:28.453Z",
+    "startedAt": "2026-05-08T01:03:41.095Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 0,
+    "failedLinks": 1,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-08T01:04:38.947Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-6c49-7341-9363-423c6ce55e0a",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://en.wikipedia.org/wiki/C%2B%2B"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://en.wikipedia.org/wiki/C%2B%2B.",
+    "runtimeTaskId": "d17f5e9cca9b47afb87334079e97a6e6",
+    "createdAt": "2026-04-30T07:47:29.483Z",
+    "startedAt": "2026-05-08T01:03:48.111Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-08T01:04:04.794Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-703b-7478-8766-570ec3638bbe",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://en.wikipedia.org/w/index.php?search=machine+learning"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://en.wikipedia.org/w/index.php?search=machine+learning.",
+    "runtimeTaskId": "be10b3df9ac94abdb75f1f57d352e63e",
+    "createdAt": "2026-04-30T07:47:30.492Z",
+    "startedAt": "2026-05-08T01:04:09.857Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-08T01:04:53.385Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-7450-74cd-84fa-98cdaf478e29",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://a.com?b=2&amp;a=1"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://a.com?b=2&amp;a=1.",
+    "runtimeTaskId": "15bb7de2e5cf438389b632dac25a3527",
+    "createdAt": "2026-04-30T07:47:31.538Z",
+    "startedAt": "2026-05-08T01:05:01.977Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 0,
+    "failedLinks": 1,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-08T01:05:48.630Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-7852-7258-bd79-ecd3dc6d03bb",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://www.save.ca/flyers/"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://www.save.ca/flyers/.",
+    "runtimeTaskId": "f2c181bac32d48cb8fee4dd008d54964",
+    "createdAt": "2026-04-30T07:47:32.563Z",
+    "startedAt": "2026-05-08T01:05:09.998Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-08T01:05:26.604Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-7cca-7679-a370-5eae09feddc2",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://www.buzzfeed.com/ca"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://www.buzzfeed.com/ca.",
+    "runtimeTaskId": "c3077b74a1334a80bf27782041b07fbd",
+    "createdAt": "2026-04-30T07:47:33.708Z",
+    "startedAt": "2026-05-08T04:12:16.512Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 348,
+    "uniqueLinks": 286,
+    "processedLinks": 1,
+    "failedLinks": 1,
+    "excludedLinks": 12,
+    "duplicateLinks": 334,
+    "depth": 1,
+    "completedAt": "2026-05-08T05:01:52.729Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-80d9-7056-8718-af96cd1a75d6",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://globo.com"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://globo.com.",
+    "runtimeTaskId": "2d58b8f205e24826933fc56bc1ee0589",
+    "createdAt": "2026-04-30T07:47:34.747Z",
+    "startedAt": "2026-05-08T04:20:30.096Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 0,
+    "uniqueLinks": 0,
+    "processedLinks": 0,
+    "failedLinks": 1,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 1,
+    "completedAt": "2026-05-08T04:26:02.029Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-8501-7620-9ac3-1cbd721ab356",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://www.hsbc.com/"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://www.hsbc.com/.",
+    "runtimeTaskId": "e8592a645c8245158ee4dc6bbc36f329",
+    "createdAt": "2026-04-30T07:47:35.810Z",
+    "startedAt": "2026-05-08T04:24:48.055Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 207,
+    "uniqueLinks": 127,
+    "processedLinks": 3,
+    "failedLinks": 104,
+    "excludedLinks": 9,
+    "duplicateLinks": 91,
+    "depth": 1,
+    "completedAt": "2026-05-08T05:16:34.878Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-892e-7604-8f79-92277ba55266",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://theinformr.com"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://theinformr.com.",
+    "runtimeTaskId": "bad12c5108d840ca99032b36e08b289b",
+    "createdAt": "2026-04-30T07:47:36.879Z",
+    "startedAt": "2026-05-08T04:27:38.980Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 0,
+    "uniqueLinks": 0,
+    "processedLinks": 0,
+    "failedLinks": 1,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 1,
+    "completedAt": "2026-05-08T04:29:07.017Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-8d37-74a9-9161-b609b6f2100d",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://simplerate.ca"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://simplerate.ca.",
+    "runtimeTaskId": "b4332ab92f99471ea079e052b9a4f9e6",
+    "createdAt": "2026-04-30T07:47:37.912Z",
+    "startedAt": "2026-05-08T04:30:41.197Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 0,
+    "uniqueLinks": 0,
+    "processedLinks": 0,
+    "failedLinks": 1,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 1,
+    "completedAt": "2026-05-08T04:31:20.341Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-915e-75eb-83c8-b4029284ce31",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://atila.ca"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://atila.ca.",
+    "runtimeTaskId": "eb85beb17ab348f195969a46175271d5",
+    "createdAt": "2026-04-30T07:47:38.976Z",
+    "startedAt": "2026-05-08T04:32:59.677Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 128,
+    "uniqueLinks": 72,
+    "processedLinks": 52,
+    "failedLinks": 2,
+    "excludedLinks": 18,
+    "duplicateLinks": 55,
+    "depth": 1,
+    "completedAt": "2026-05-08T04:38:40.647Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-957a-721f-a17d-6654db9c1575",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://apnews.com/"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://apnews.com/.",
+    "runtimeTaskId": "bc40771ef1484306817eaf50d7a00627",
+    "createdAt": "2026-04-30T07:47:40.028Z",
+    "startedAt": "2026-05-08T04:40:15.969Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 1600,
+    "uniqueLinks": 315,
+    "processedLinks": 266,
+    "failedLinks": 2,
+    "excludedLinks": 39,
+    "duplicateLinks": 1292,
+    "depth": 1,
+    "completedAt": "2026-05-08T07:24:11.334Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-9986-740c-9dbb-95c33c94a5a6",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://moneyeh.ca/"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://moneyeh.ca/.",
+    "runtimeTaskId": "8d4f6699d72a450bb22bf5b63a5a4bdd",
+    "createdAt": "2026-04-30T07:47:41.064Z",
+    "startedAt": "2026-05-08T04:40:55.721Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 84,
+    "uniqueLinks": 55,
+    "processedLinks": 0,
+    "failedLinks": 0,
+    "excludedLinks": 2,
+    "duplicateLinks": 81,
+    "depth": 1,
+    "completedAt": "2026-05-08T04:44:06.918Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-9d7d-70e9-b3c8-7e816c78b548",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://www.buzzfeed.com/ca"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://www.buzzfeed.com/ca.",
+    "runtimeTaskId": "1800e9d0779841c3a247f7f94848d152",
+    "createdAt": "2026-04-30T07:47:42.078Z",
+    "startedAt": "2026-05-08T04:45:41.087Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 348,
+    "uniqueLinks": 287,
+    "processedLinks": 1,
+    "failedLinks": 1,
+    "excludedLinks": 12,
+    "duplicateLinks": 334,
+    "depth": 1,
+    "completedAt": "2026-05-08T05:41:44.811Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-a165-7538-bce5-13a3edaea1d2",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://crawldemolinksnew.signitydemo.in"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://crawldemolinksnew.signitydemo.in.",
+    "runtimeTaskId": "0cf3563874da4985a4fcb0b0435f8bdf",
+    "createdAt": "2026-04-30T07:47:43.079Z",
+    "startedAt": "2026-05-08T05:02:58.820Z",
+    "enabledLinkDiscovery": true,
+    "totalLinks": 14,
+    "uniqueLinks": 10,
+    "processedLinks": 3,
+    "failedLinks": 2,
+    "excludedLinks": 6,
+    "duplicateLinks": 3,
+    "depth": 1,
+    "completedAt": "2026-05-08T05:04:14.639Z"
+}</t>
+  </si>
+  <si>
+    <t>019e1adc-1127-75c4-8387-3542cd1f216d</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1adc-1127-75c4-8387-3542cd1f216d"
+}</t>
+  </si>
+  <si>
+    <t>019e1adc-1765-76fc-a763-4124a5575669</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1adc-1765-76fc-a763-4124a5575669"
+}</t>
+  </si>
+  <si>
+    <t>019e1adc-1c12-76eb-8be0-32d8bca4d597</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1adc-1c12-76eb-8be0-32d8bca4d597"
+}</t>
+  </si>
+  <si>
+    <t>019e1adc-20e3-71ae-8e6a-b2e095910d5a</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1adc-20e3-71ae-8e6a-b2e095910d5a"
+}</t>
+  </si>
+  <si>
+    <t>019e1adc-2565-77de-95cd-62e101e6b8b6</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1adc-2565-77de-95cd-62e101e6b8b6"
+}</t>
+  </si>
+  <si>
+    <t>019e1adc-2ad6-766b-9413-c05f1cdf5591</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1adc-2ad6-766b-9413-c05f1cdf5591"
+}</t>
+  </si>
+  <si>
+    <t>019e1adc-2f7f-71fc-9819-3cfef175f760</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1adc-2f7f-71fc-9819-3cfef175f760"
+}</t>
+  </si>
+  <si>
+    <t>019e1adc-340c-724c-a750-64c674309d02</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1adc-340c-724c-a750-64c674309d02"
+}</t>
+  </si>
+  <si>
+    <t>019e1adc-396d-7698-a1ed-ec7dfcd331b5</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1adc-396d-7698-a1ed-ec7dfcd331b5"
+}</t>
+  </si>
+  <si>
+    <t>019e1adc-3e8f-7618-b434-a67d33efc7cd</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1adc-3e8f-7618-b434-a67d33efc7cd"
+}</t>
+  </si>
+  <si>
+    <t>019e1adc-43ea-76eb-9ea7-96ad9796db16</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1adc-43ea-76eb-9ea7-96ad9796db16"
+}</t>
+  </si>
+  <si>
+    <t>019e1adc-48c4-758e-9d11-1114ac601df7</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1adc-48c4-758e-9d11-1114ac601df7"
+}</t>
+  </si>
+  <si>
+    <t>019e1adc-4e35-7371-8838-fb9c3a3d98d9</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1adc-4e35-7371-8838-fb9c3a3d98d9"
+}</t>
+  </si>
+  <si>
+    <t>019e1adc-52c4-7212-b797-922492149dce</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1adc-52c4-7212-b797-922492149dce"
+}</t>
+  </si>
+  <si>
+    <t>019e1adc-5750-743b-837b-ad3f8e320465</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1adc-5750-743b-837b-ad3f8e320465"
+}</t>
+  </si>
+  <si>
+    <t>019e1adc-5d7f-72dd-8543-7a9ff1982d28</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1adc-5d7f-72dd-8543-7a9ff1982d28"
+}</t>
+  </si>
+  <si>
+    <t>019e1adc-61fd-7395-9991-6af0a2e661dc</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1adc-61fd-7395-9991-6af0a2e661dc"
+}</t>
+  </si>
+  <si>
+    <t>019e1adc-6720-77af-9886-6b145aa42551</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1adc-6720-77af-9886-6b145aa42551"
+}</t>
+  </si>
+  <si>
+    <t>019e1adc-6bfc-707c-a0f6-c25829015906</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1adc-6bfc-707c-a0f6-c25829015906"
+}</t>
+  </si>
+  <si>
+    <t>019e1adc-720f-7108-9650-607239f6a3fa</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1adc-720f-7108-9650-607239f6a3fa"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-51f6-70f1-948b-5ff8f9b2af4f",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://en.wikipedia.org/wiki/Category:Machine_learning_algorithms"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://en.wikipedia.org/wiki/Category:Machine_learning_algorithms.",
+    "runtimeTaskId": "e21c21ff79814006bbda6954b7a4a3e1",
+    "createdAt": "2026-04-30T07:47:22.745Z",
+    "startedAt": "2026-05-12T03:27:48.871Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-12T03:28:06.370Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-578c-734b-84cf-2030acc3c26c",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://en.wikipedia.org/wiki/Category:Artificial_intelligence"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://en.wikipedia.org/wiki/Category:Artificial_intelligence.",
+    "runtimeTaskId": "cb804da0d0ed48dea8b034ae3dc8fe20",
+    "createdAt": "2026-04-30T07:47:24.175Z",
+    "startedAt": "2026-05-12T03:29:05.278Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-12T03:29:25.691Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-5bdb-70fa-9d0f-230890e4485d",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://en.wikipedia.org/wiki/Special:Search?search=Machine%20Learning"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://en.wikipedia.org/wiki/Special:Search?search=Machine%20Learning.",
+    "runtimeTaskId": "13cf738998ad415c89699434f1a76656",
+    "createdAt": "2026-04-30T07:47:25.277Z",
+    "startedAt": "2026-05-12T03:29:59.892Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-12T03:30:33.420Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-5ff2-763d-9bba-0751e3a5ceec",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://en.wikipedia.org/w/index.php?search=Research&amp;title=Special:Search"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://en.wikipedia.org/w/index.php?search=Research&amp;title=Special:Search.",
+    "runtimeTaskId": "ecd3896543ed4c26bf70de4323f88c51",
+    "createdAt": "2026-04-30T07:47:26.324Z",
+    "startedAt": "2026-05-12T03:30:10.278Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-12T03:30:31.044Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-642b-736d-91b8-65d85b6310ec",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://en.wikipedia.org/w/index.php?search=Java_(programming_language)&amp;title=Special:Search"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://en.wikipedia.org/w/index.php?search=Java_(programming_language)&amp;title=Special:Search.",
+    "runtimeTaskId": "84207cc443254c719418219df29f1f2c",
+    "createdAt": "2026-04-30T07:47:27.405Z",
+    "startedAt": "2026-05-12T03:31:08.754Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-12T03:31:42.157Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-6842-75eb-b48e-74be2784511c",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "HTTP://EXAMPL.COM:80/"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for HTTP://EXAMPL.COM:80/.",
+    "runtimeTaskId": "54ed1ab68c8d4e8ba7682bdc50a83ca7",
+    "createdAt": "2026-04-30T07:47:28.453Z",
+    "startedAt": "2026-05-12T03:32:04.202Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-12T03:33:16.953Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-6c49-7341-9363-423c6ce55e0a",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://en.wikipedia.org/wiki/C%2B%2B"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://en.wikipedia.org/wiki/C%2B%2B.",
+    "runtimeTaskId": "bb5efe71f3c8488aa53b43528254ef7d",
+    "createdAt": "2026-04-30T07:47:29.483Z",
+    "startedAt": "2026-05-12T03:32:17.415Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-12T03:32:37.434Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-703b-7478-8766-570ec3638bbe",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://en.wikipedia.org/w/index.php?search=machine+learning"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://en.wikipedia.org/w/index.php?search=machine+learning.",
+    "runtimeTaskId": "e9717b9434d64668bcd74162348830e2",
+    "createdAt": "2026-04-30T07:47:30.492Z",
+    "startedAt": "2026-05-12T03:32:46.193Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-12T03:33:12.950Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-7450-74cd-84fa-98cdaf478e29",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://a.com?b=2&amp;a=1"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://a.com?b=2&amp;a=1.",
+    "runtimeTaskId": "aa49a4c4f6bb41a1a67cd42bc38ac3a7",
+    "createdAt": "2026-04-30T07:47:31.538Z",
+    "startedAt": "2026-05-12T03:32:44.574Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 0,
+    "failedLinks": 1,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-12T03:33:30.938Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019ddd5b-7852-7258-bd79-ecd3dc6d03bb",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://www.save.ca/flyers/"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://www.save.ca/flyers/.",
+    "runtimeTaskId": "7c2da663f3554b42bda92c0de2cb0400",
+    "createdAt": "2026-04-30T07:47:32.563Z",
+    "startedAt": "2026-05-12T03:33:17.529Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-12T03:33:34.283Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-1127-75c4-8387-3542cd1f216d",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "http://creditcardsforbadcredit.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for http://creditcardsforbadcredit.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-1765-76fc-a763-4124a5575669",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://bestcards.com"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://bestcards.com"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-1c12-76eb-8be0-32d8bca4d597",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://bestmoney.com"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://bestmoney.com"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-20e3-71ae-8e6a-b2e095910d5a",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://bestrates.com"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://bestrates.com"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-2565-77de-95cd-62e101e6b8b6",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "http://investingforretirement.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for http://investingforretirement.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-2ad6-766b-9413-c05f1cdf5591",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://allcards.com"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://allcards.com"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-2f7f-71fc-9819-3cfef175f760",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://atila.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://atila.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-340c-724c-a750-64c674309d02",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://apnews.com"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://apnews.com"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-396d-7698-a1ed-ec7dfcd331b5",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://hardbacon.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://hardbacon.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-3e8f-7618-b434-a67d33efc7cd",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://accuradio.co"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://accuradio.co"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-43ea-76eb-9ea7-96ad9796db16",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://azlyrics.com"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://azlyrics.com"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-48c4-758e-9d11-1114ac601df7",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "http://howtosavemoney.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for http://howtosavemoney.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-4e35-7371-8838-fb9c3a3d98d9",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://blog.rewardscanada.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://blog.rewardscanada.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-52c4-7212-b797-922492149dce",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://borrowell.com"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://borrowell.com"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-5750-743b-837b-ad3f8e320465",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://broadmoney.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://broadmoney.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-5d7f-72dd-8543-7a9ff1982d28",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://brokersplaybook.activehosted.co"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://brokersplaybook.activehosted.co"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-61fd-7395-9991-6af0a2e661dc",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://app.clearscore.com"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://app.clearscore.com"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-6720-77af-9886-6b145aa42551",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://buildwealthcanada.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://buildwealthcanada.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-6bfc-707c-a0f6-c25829015906",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://canadianbudget.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://canadianbudget.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-720f-7108-9650-607239f6a3fa",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://canadian-reviews.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://canadian-reviews.ca"
+}</t>
+  </si>
+  <si>
+    <t>019e1adf-f6d1-7185-b4b2-63ab4871997b</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1adf-f6d1-7185-b4b2-63ab4871997b"
+}</t>
+  </si>
+  <si>
+    <t>019e1adf-fcc4-7206-815a-620c3fecda4a</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1adf-fcc4-7206-815a-620c3fecda4a"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae0-012a-729b-86aa-a0ad4f3fc9e7</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae0-012a-729b-86aa-a0ad4f3fc9e7"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae0-0581-716b-8973-97454be2e421</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae0-0581-716b-8973-97454be2e421"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae0-09fb-7381-ac1e-1fe8fdeebe21</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae0-09fb-7381-ac1e-1fe8fdeebe21"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae0-0e7b-7170-a090-a0361d71e1ce</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae0-0e7b-7170-a090-a0361d71e1ce"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae0-134a-7654-bf9a-17121a3652aa</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae0-134a-7654-bf9a-17121a3652aa"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae0-179b-744c-8476-58485e373fb7</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae0-179b-744c-8476-58485e373fb7"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae0-1bee-71bf-abf3-d4fcccb9cea4</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae0-1bee-71bf-abf3-d4fcccb9cea4"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae0-202e-75ac-a911-bdb563e63a8b</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae0-202e-75ac-a911-bdb563e63a8b"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae0-247f-77cf-9b0a-0a0d0268d05d</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae0-247f-77cf-9b0a-0a0d0268d05d"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae0-292b-748b-89ff-5f67e211afa8</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae0-292b-748b-89ff-5f67e211afa8"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae0-2da0-74db-b61f-6232a9e03c87</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae0-2da0-74db-b61f-6232a9e03c87"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae0-34cd-7649-a5d5-4a0fcb2ac316</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae0-34cd-7649-a5d5-4a0fcb2ac316"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae0-3a00-732e-85b0-faf81f2345bc</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae0-3a00-732e-85b0-faf81f2345bc"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae0-3ea3-7602-807b-cc1ab1d98658</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae0-3ea3-7602-807b-cc1ab1d98658"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae0-430f-76ed-9184-748cda3dc370</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae0-430f-76ed-9184-748cda3dc370"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae0-478e-7567-ab4a-8bab23835968</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae0-478e-7567-ab4a-8bab23835968"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae0-4c68-7618-b7c3-2e060086cc50</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae0-4c68-7618-b7c3-2e060086cc50"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae0-50df-710d-9728-770dc686b55a</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae0-50df-710d-9728-770dc686b55a"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-1127-75c4-8387-3542cd1f216d",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "http://creditcardsforbadcredit.ca"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for http://creditcardsforbadcredit.ca.",
+    "runtimeTaskId": "dbbe0497cb4a4230b3dfe2c9c66d6899",
+    "createdAt": "2026-05-12T06:24:50.473Z",
+    "startedAt": "2026-05-12T06:27:57.703Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-12T06:28:12.949Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-1765-76fc-a763-4124a5575669",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://bestcards.com"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://bestcards.com.",
+    "runtimeTaskId": "4de5b932750746bf93c9f9e9571a0d0e",
+    "createdAt": "2026-05-12T06:24:52.071Z",
+    "startedAt": "2026-05-12T06:28:43.288Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-12T06:28:58.649Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adf-f6d1-7185-b4b2-63ab4871997b",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://canoe.com"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://canoe.com"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adf-fcc4-7206-815a-620c3fecda4a",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://cashback.highinterestsavings.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://cashback.highinterestsavings.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae0-012a-729b-86aa-a0ad4f3fc9e7",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://cardbenefit.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://cardbenefit.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae0-0581-716b-8973-97454be2e421",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://cellphones.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://cellphones.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae0-09fb-7381-ac1e-1fe8fdeebe21",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://cleveland.com"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://cleveland.com"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae0-0e7b-7170-a090-a0361d71e1ce",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://click.wonderlist.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://click.wonderlist.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae0-134a-7654-bf9a-17121a3652aa",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://comparewise.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://comparewise.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae0-179b-744c-8476-58485e373fb7",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://courses.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://courses.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae0-1bee-71bf-abf3-d4fcccb9cea4",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://creditcardgenius.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://creditcardgenius.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae0-202e-75ac-a911-bdb563e63a8b",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://creditcards.redflagdeals.co"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://creditcards.redflagdeals.co"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae0-247f-77cf-9b0a-0a0d0268d05d",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://creditcards.smartcanucks.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://creditcards.smartcanucks.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae0-292b-748b-89ff-5f67e211afa8",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://creditdonkey.com"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://creditdonkey.com"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae0-2da0-74db-b61f-6232a9e03c87",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://creditkarma.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://creditkarma.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae0-34cd-7649-a5d5-4a0fcb2ac316",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://credit-land.com"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://credit-land.com"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae0-3a00-732e-85b0-faf81f2345bc",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://creditcardsforbadcredit.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://creditcardsforbadcredit.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae0-3ea3-7602-807b-cc1ab1d98658",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://current.com"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://current.com"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae0-430f-76ed-9184-748cda3dc370",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://creditnest.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://creditnest.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae0-478e-7567-ab4a-8bab23835968",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://daytrading.com"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://daytrading.com"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae0-4c68-7618-b7c3-2e060086cc50",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://dealmoon.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://dealmoon.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae0-50df-710d-9728-770dc686b55a",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://exploreficanada.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://exploreficanada.ca"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae3-2983-7045-8723-505954883340</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae3-2983-7045-8723-505954883340"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae3-3023-72d2-b3a4-6a7c8e750cb2</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae3-3023-72d2-b3a4-6a7c8e750cb2"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae3-356f-75fe-b7ba-aa1d227e52ec</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae3-356f-75fe-b7ba-aa1d227e52ec"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae3-3b16-747f-8f8c-b292f5acf03d</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae3-3b16-747f-8f8c-b292f5acf03d"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae3-4056-74bd-852a-5dfd1616d4f4</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae3-4056-74bd-852a-5dfd1616d4f4"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae3-45d6-75bb-8ce1-20ccb2a8036a</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae3-45d6-75bb-8ce1-20ccb2a8036a"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae3-4b36-75f8-9231-55f5e10f4de3</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae3-4b36-75f8-9231-55f5e10f4de3"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae3-5067-7519-94e4-36037ee2c75f</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae3-5067-7519-94e4-36037ee2c75f"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae3-5986-730a-b183-ee29d7a6791d</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae3-5986-730a-b183-ee29d7a6791d"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae3-5f45-73df-87f3-2e64297caf51</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae3-5f45-73df-87f3-2e64297caf51"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae3-668d-701c-8473-457623851b6a</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae3-668d-701c-8473-457623851b6a"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae3-6c1a-76bb-864b-908b84b11275</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae3-6c1a-76bb-864b-908b84b11275"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae3-728e-7178-b43b-5cfe1b7a5233</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae3-728e-7178-b43b-5cfe1b7a5233"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae3-7800-768c-ba63-e65ec99b04d9</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae3-7800-768c-ba63-e65ec99b04d9"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae3-7da5-71fe-a431-5a7a62d69939</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae3-7da5-71fe-a431-5a7a62d69939"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae3-82d4-77b9-91c5-3e72a62a27aa</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae3-82d4-77b9-91c5-3e72a62a27aa"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae3-9170-7540-9d7c-674c70ebf712</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae3-9170-7540-9d7c-674c70ebf712"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae3-96ae-7168-89c9-24139f32a874</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae3-96ae-7168-89c9-24139f32a874"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae3-9c57-715c-bc4e-1d85ddd7ea8f</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae3-9c57-715c-bc4e-1d85ddd7ea8f"
+}</t>
+  </si>
+  <si>
+    <t>019e1ae3-a119-72be-bd78-3ab330bbc1d1</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Crawl job created successfully.",
+    "jobId": "019e1ae3-a119-72be-bd78-3ab330bbc1d1"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-1c12-76eb-8be0-32d8bca4d597",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://bestmoney.com"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://bestmoney.com.",
+    "runtimeTaskId": "c9a95d69e2d44e8998b9974c0d8af3b4",
+    "createdAt": "2026-05-12T06:24:53.268Z",
+    "startedAt": "2026-05-12T06:30:45.814Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-12T06:31:03.366Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-20e3-71ae-8e6a-b2e095910d5a",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://bestrates.com"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://bestrates.com.",
+    "runtimeTaskId": "a10248acc6b641d89d04f080f8430277",
+    "createdAt": "2026-05-12T06:24:54.501Z",
+    "startedAt": "2026-05-12T06:32:44.422Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-12T06:32:58.292Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-2565-77de-95cd-62e101e6b8b6",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "http://investingforretirement.ca"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for http://investingforretirement.ca.",
+    "runtimeTaskId": "e20cea5ec91e49c5b46dcaa076c601e2",
+    "createdAt": "2026-05-12T06:24:55.655Z",
+    "startedAt": "2026-05-12T06:34:40.375Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-12T06:34:56.585Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-2ad6-766b-9413-c05f1cdf5591",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://allcards.com"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://allcards.com.",
+    "runtimeTaskId": "6d84d9aa2d8f4977ab5a60f1c87f1746",
+    "createdAt": "2026-05-12T06:24:57.047Z",
+    "startedAt": "2026-05-12T06:36:33.900Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 0,
+    "failedLinks": 1,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-12T06:36:45.885Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-2f7f-71fc-9819-3cfef175f760",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://atila.ca"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://atila.ca.",
+    "runtimeTaskId": "930b1a1dc9cd418cb6314adbce1e545c",
+    "createdAt": "2026-05-12T06:24:58.241Z",
+    "startedAt": "2026-05-12T06:38:24.436Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-12T06:38:49.624Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae3-2983-7045-8723-505954883340",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://earnandburn.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://earnandburn.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae3-3023-72d2-b3a4-6a7c8e750cb2",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://familytaxrecovery.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://familytaxrecovery.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae3-356f-75fe-b7ba-aa1d227e52ec",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://feeds.buzzsprout.co"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://feeds.buzzsprout.co"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae3-3b16-747f-8f8c-b292f5acf03d",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://finances.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://finances.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae3-4056-74bd-852a-5dfd1616d4f4",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://financebuzz.com"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://financebuzz.com"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae3-45d6-75bb-8ce1-20ccb2a8036a",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://fintechlabs.com"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://fintechlabs.com"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae3-4b36-75f8-9231-55f5e10f4de3",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://finanso.com"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://finanso.com"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae3-5067-7519-94e4-36037ee2c75f",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://forums.redflagdeals.com"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://forums.redflagdeals.com"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae3-5986-730a-b183-ee29d7a6791d",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://flyers.smartcanucks.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://flyers.smartcanucks.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae3-5f45-73df-87f3-2e64297caf51",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://fnbo.com"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://fnbo.com"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae3-668d-701c-8473-457623851b6a",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://forbes.com"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://forbes.com"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae3-6c1a-76bb-864b-908b84b11275",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://frugalflyer.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://frugalflyer.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae3-728e-7178-b43b-5cfe1b7a5233",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://georgeneufeld.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://georgeneufeld.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae3-7800-768c-ba63-e65ec99b04d9",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://genymoney.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://genymoney.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae3-7da5-71fe-a431-5a7a62d69939",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://go.movingwaldo.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://go.movingwaldo.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae3-82d4-77b9-91c5-3e72a62a27aa",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://go.myratecompass.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://go.myratecompass.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae3-9170-7540-9d7c-674c70ebf712",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://greatcanadianrebates.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://greatcanadianrebates.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae3-96ae-7168-89c9-24139f32a874",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://greenfi.co"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://greenfi.co"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae3-9c57-715c-bc4e-1d85ddd7ea8f",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://hellosafe.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://hellosafe.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1ae3-a119-72be-bd78-3ab330bbc1d1",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://highinterestsavings.ca"
+    ],
+    "status": "queued",
+    "message": "Crawling process is queued for https://highinterestsavings.ca"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-340c-724c-a750-64c674309d02",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://apnews.com"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://apnews.com.",
+    "runtimeTaskId": "f50cc75133374d8b8e5faf32a096300d",
+    "createdAt": "2026-05-12T06:24:59.406Z",
+    "startedAt": "2026-05-12T06:40:23.507Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-12T06:40:58.383Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-396d-7698-a1ed-ec7dfcd331b5",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://hardbacon.ca"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://hardbacon.ca.",
+    "runtimeTaskId": "d38581967b21450685a675f4623fe6f4",
+    "createdAt": "2026-05-12T06:25:00.783Z",
+    "startedAt": "2026-05-12T06:42:50.652Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 0,
+    "failedLinks": 1,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-12T06:43:05.686Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-3e8f-7618-b434-a67d33efc7cd",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://accuradio.co"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://accuradio.co.",
+    "runtimeTaskId": "cd2164c45f4e430f9b401686e43d3247",
+    "createdAt": "2026-05-12T06:25:02.097Z",
+    "startedAt": "2026-05-12T06:44:45.856Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-12T06:44:58.567Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-43ea-76eb-9ea7-96ad9796db16",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://azlyrics.com"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://azlyrics.com.",
+    "runtimeTaskId": "fac88f09802e4f15913934b4349e996b",
+    "createdAt": "2026-05-12T06:25:03.468Z",
+    "startedAt": "2026-05-12T06:48:29.349Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 0,
+    "failedLinks": 1,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-12T06:48:41.414Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-48c4-758e-9d11-1114ac601df7",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "http://howtosavemoney.ca"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for http://howtosavemoney.ca.",
+    "runtimeTaskId": "7f9f9a80ca144bcfaebe4354c59871e0",
+    "createdAt": "2026-05-12T06:25:04.709Z",
+    "startedAt": "2026-05-12T06:50:25.943Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 0,
+    "failedLinks": 1,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-12T06:50:37.836Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-4e35-7371-8838-fb9c3a3d98d9",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://blog.rewardscanada.ca"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://blog.rewardscanada.ca.",
+    "runtimeTaskId": "dc09d72076fa4017a3ee46b11b9ebd19",
+    "createdAt": "2026-05-12T06:25:06.103Z",
+    "startedAt": "2026-05-12T06:52:30.969Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-12T06:52:46.522Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-52c4-7212-b797-922492149dce",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://borrowell.com"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://borrowell.com.",
+    "runtimeTaskId": "29a234d06dba4b20888085e15f2905bf",
+    "createdAt": "2026-05-12T06:25:07.270Z",
+    "startedAt": "2026-05-12T06:53:11.979Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-12T06:53:29.382Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-5750-743b-837b-ad3f8e320465",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://broadmoney.ca"
+    ],
+    "status": "running",
+    "message": "Crawling process is running for https://broadmoney.ca",
+    "runtimeTaskId": "0b0a9ef01fca44308e475c1aa07d3f8d",
+    "createdAt": "2026-05-12T06:25:08.434Z",
+    "startedAt": "2026-05-12T06:54:30.468Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 0,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-5750-743b-837b-ad3f8e320465",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://broadmoney.ca"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://broadmoney.ca.",
+    "runtimeTaskId": "0b0a9ef01fca44308e475c1aa07d3f8d",
+    "createdAt": "2026-05-12T06:25:08.434Z",
+    "startedAt": "2026-05-12T06:54:30.468Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 1,
+    "failedLinks": 0,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-12T06:54:43.705Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "jobId": "019e1adc-5d7f-72dd-8543-7a9ff1982d28",
+    "merchantId": "merchant_simar",
+    "domain": [
+        "https://brokersplaybook.activehosted.co"
+    ],
+    "status": "completed",
+    "message": "Crawling process is successfully completed for https://brokersplaybook.activehosted.co.",
+    "runtimeTaskId": "b359d753098145dcb49aeb898da1cd37",
+    "createdAt": "2026-05-12T06:25:10.016Z",
+    "startedAt": "2026-05-12T06:56:28.985Z",
+    "enabledLinkDiscovery": false,
+    "totalLinks": 1,
+    "uniqueLinks": 1,
+    "processedLinks": 0,
+    "failedLinks": 1,
+    "excludedLinks": 0,
+    "duplicateLinks": 0,
+    "depth": 0,
+    "completedAt": "2026-05-12T06:56:43.135Z"
 }</t>
   </si>
 </sst>
@@ -827,7 +4031,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95DF0F3A-A575-4E1C-BD31-366F2E5919E5}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="37.5546875"/>
@@ -1062,6 +4266,666 @@
         <v>41</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="B22" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="B23" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="B24" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="B25" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="B26" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="B27" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="B28" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="B29" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="B30" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="B31" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="B32" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="B33" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="B34" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="B35" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="B36" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="B37" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="B38" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="B39" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C39" t="s" s="0">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="B40" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C40" t="s" s="0">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="B41" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C41" t="s" s="0">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>198</v>
+      </c>
+      <c r="B42" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C42" t="s" s="0">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="B43" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>202</v>
+      </c>
+      <c r="B44" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B45" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C45" t="s" s="0">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B46" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C46" t="s" s="0">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B47" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C47" t="s" s="0">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>210</v>
+      </c>
+      <c r="B48" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C48" t="s" s="0">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B49" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C49" t="s" s="0">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B50" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C50" t="s" s="0">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="B51" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C51" t="s" s="0">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>218</v>
+      </c>
+      <c r="B52" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C52" t="s" s="0">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>220</v>
+      </c>
+      <c r="B53" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C53" t="s" s="0">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>222</v>
+      </c>
+      <c r="B54" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C54" t="s" s="0">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="B55" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C55" t="s" s="0">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>226</v>
+      </c>
+      <c r="B56" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C56" t="s" s="0">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>228</v>
+      </c>
+      <c r="B57" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C57" t="s" s="0">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>230</v>
+      </c>
+      <c r="B58" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C58" t="s" s="0">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="B59" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C59" t="s" s="0">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>234</v>
+      </c>
+      <c r="B60" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C60" t="s" s="0">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="0">
+        <v>236</v>
+      </c>
+      <c r="B61" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C61" t="s" s="0">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="0">
+        <v>260</v>
+      </c>
+      <c r="B62" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C62" t="s" s="0">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="0">
+        <v>262</v>
+      </c>
+      <c r="B63" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C63" t="s" s="0">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="0">
+        <v>264</v>
+      </c>
+      <c r="B64" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C64" t="s" s="0">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="0">
+        <v>266</v>
+      </c>
+      <c r="B65" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C65" t="s" s="0">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="0">
+        <v>268</v>
+      </c>
+      <c r="B66" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C66" t="s" s="0">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="0">
+        <v>270</v>
+      </c>
+      <c r="B67" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C67" t="s" s="0">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="0">
+        <v>272</v>
+      </c>
+      <c r="B68" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C68" t="s" s="0">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="0">
+        <v>274</v>
+      </c>
+      <c r="B69" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C69" t="s" s="0">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="0">
+        <v>276</v>
+      </c>
+      <c r="B70" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C70" t="s" s="0">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="0">
+        <v>278</v>
+      </c>
+      <c r="B71" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C71" t="s" s="0">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="0">
+        <v>280</v>
+      </c>
+      <c r="B72" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C72" t="s" s="0">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="0">
+        <v>282</v>
+      </c>
+      <c r="B73" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C73" t="s" s="0">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="0">
+        <v>284</v>
+      </c>
+      <c r="B74" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C74" t="s" s="0">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="0">
+        <v>286</v>
+      </c>
+      <c r="B75" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C75" t="s" s="0">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="0">
+        <v>288</v>
+      </c>
+      <c r="B76" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C76" t="s" s="0">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="0">
+        <v>290</v>
+      </c>
+      <c r="B77" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C77" t="s" s="0">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="0">
+        <v>292</v>
+      </c>
+      <c r="B78" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C78" t="s" s="0">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="0">
+        <v>294</v>
+      </c>
+      <c r="B79" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C79" t="s" s="0">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="B80" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C80" t="s" s="0">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="0">
+        <v>298</v>
+      </c>
+      <c r="B81" t="n" s="0">
+        <v>201.0</v>
+      </c>
+      <c r="C81" t="s" s="0">
+        <v>299</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1070,7 +4934,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1092,13 +4956,13 @@
         <v>2</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>200.0</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>46</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3">
@@ -1106,13 +4970,13 @@
         <v>4</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>200.0</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>47</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4">
@@ -1120,13 +4984,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>200.0</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>48</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5">
@@ -1134,13 +4998,13 @@
         <v>8</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>200.0</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>49</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6">
@@ -1148,13 +5012,13 @@
         <v>10</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>200.0</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>50</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7">
@@ -1162,13 +5026,13 @@
         <v>12</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>200.0</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>51</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8">
@@ -1176,13 +5040,13 @@
         <v>14</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>200.0</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>52</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9">
@@ -1190,13 +5054,13 @@
         <v>16</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="C9" t="n" s="0">
         <v>200.0</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>53</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10">
@@ -1204,13 +5068,13 @@
         <v>18</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>200.0</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>54</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -1218,13 +5082,13 @@
         <v>20</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>200.0</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>55</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1365,6 +5229,846 @@
       </c>
       <c r="D21" t="s" s="0">
         <v>65</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="C22" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="C23" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="C24" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="C25" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="C26" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="C27" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="C28" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D28" t="s" s="0">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="C29" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D29" t="s" s="0">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="C30" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D30" t="s" s="0">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="C31" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="C32" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="C33" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D33" t="s" s="0">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="C34" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D34" t="s" s="0">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="C35" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D35" t="s" s="0">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="C36" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D36" t="s" s="0">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="C37" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D37" t="s" s="0">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C38" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D38" t="s" s="0">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C39" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D39" t="s" s="0">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C40" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D40" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C41" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D41" t="s" s="0">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>198</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C42" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D42" t="s" s="0">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C43" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D43" t="s" s="0">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>202</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C44" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D44" t="s" s="0">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C45" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D45" t="s" s="0">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C46" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D46" t="s" s="0">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C47" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D47" t="s" s="0">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>210</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C48" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D48" t="s" s="0">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C49" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D49" t="s" s="0">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B50" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C50" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D50" t="s" s="0">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C51" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D51" t="s" s="0">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>218</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C52" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D52" t="s" s="0">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>220</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C53" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D53" t="s" s="0">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>222</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C54" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D54" t="s" s="0">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C55" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D55" t="s" s="0">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>226</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C56" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D56" t="s" s="0">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>228</v>
+      </c>
+      <c r="B57" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C57" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D57" t="s" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>230</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C58" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D58" t="s" s="0">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="B59" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C59" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D59" t="s" s="0">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>234</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C60" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D60" t="s" s="0">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="0">
+        <v>236</v>
+      </c>
+      <c r="B61" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C61" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D61" t="s" s="0">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="0">
+        <v>260</v>
+      </c>
+      <c r="B62" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C62" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D62" t="s" s="0">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="0">
+        <v>262</v>
+      </c>
+      <c r="B63" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C63" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D63" t="s" s="0">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="0">
+        <v>264</v>
+      </c>
+      <c r="B64" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C64" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D64" t="s" s="0">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="0">
+        <v>266</v>
+      </c>
+      <c r="B65" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C65" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D65" t="s" s="0">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="0">
+        <v>268</v>
+      </c>
+      <c r="B66" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C66" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D66" t="s" s="0">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="0">
+        <v>270</v>
+      </c>
+      <c r="B67" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C67" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D67" t="s" s="0">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="0">
+        <v>272</v>
+      </c>
+      <c r="B68" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C68" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D68" t="s" s="0">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="0">
+        <v>274</v>
+      </c>
+      <c r="B69" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C69" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D69" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="0">
+        <v>276</v>
+      </c>
+      <c r="B70" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C70" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D70" t="s" s="0">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="0">
+        <v>278</v>
+      </c>
+      <c r="B71" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C71" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D71" t="s" s="0">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="0">
+        <v>280</v>
+      </c>
+      <c r="B72" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C72" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D72" t="s" s="0">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="0">
+        <v>282</v>
+      </c>
+      <c r="B73" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C73" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D73" t="s" s="0">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="0">
+        <v>284</v>
+      </c>
+      <c r="B74" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C74" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D74" t="s" s="0">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="0">
+        <v>286</v>
+      </c>
+      <c r="B75" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C75" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D75" t="s" s="0">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="0">
+        <v>288</v>
+      </c>
+      <c r="B76" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C76" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D76" t="s" s="0">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="0">
+        <v>290</v>
+      </c>
+      <c r="B77" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C77" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D77" t="s" s="0">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="0">
+        <v>292</v>
+      </c>
+      <c r="B78" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C78" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D78" t="s" s="0">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="0">
+        <v>294</v>
+      </c>
+      <c r="B79" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C79" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D79" t="s" s="0">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="B80" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C80" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D80" t="s" s="0">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="0">
+        <v>298</v>
+      </c>
+      <c r="B81" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C81" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="D81" t="s" s="0">
+        <v>324</v>
       </c>
     </row>
   </sheetData>
